--- a/数据表/Datas/UIFormConfig_界面配置.xlsx
+++ b/数据表/Datas/UIFormConfig_界面配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t>Input</t>
+  </si>
+  <si>
+    <t>RoundHUDForm</t>
+  </si>
+  <si>
+    <t>RoundBackpackForm</t>
+  </si>
+  <si>
+    <t>Backpack</t>
   </si>
 </sst>
 </file>
@@ -1394,11 +1403,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.8916666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
     <col min="3" max="4" width="22" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="1" customWidth="1"/>
     <col min="6" max="6" width="30" style="1" customWidth="1"/>
@@ -1591,6 +1600,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" customHeight="1" spans="1:6">
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:6">
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/数据表/Datas/UIFormConfig_界面配置.xlsx
+++ b/数据表/Datas/UIFormConfig_界面配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>Backpack</t>
+  </si>
+  <si>
+    <t>RoundSettlementForm</t>
   </si>
 </sst>
 </file>
@@ -1403,14 +1406,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5833333333333" style="1" customWidth="1"/>
     <col min="3" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.6666666666667" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1634,6 +1637,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13" customHeight="1" spans="1:6">
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/数据表/Datas/UIFormConfig_界面配置.xlsx
+++ b/数据表/Datas/UIFormConfig_界面配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>RoundSettlementForm</t>
+  </si>
+  <si>
+    <t>DeploymentBriefingForm</t>
+  </si>
+  <si>
+    <t>FadeForm</t>
   </si>
 </sst>
 </file>
@@ -1406,12 +1412,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="4" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.0833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.5833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.6666666666667" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
@@ -1654,6 +1661,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" customHeight="1" spans="1:6">
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:6">
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/数据表/Datas/UIFormConfig_界面配置.xlsx
+++ b/数据表/Datas/UIFormConfig_界面配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -171,6 +171,12 @@
   </si>
   <si>
     <t>FadeForm</t>
+  </si>
+  <si>
+    <t>ItemDragOverlayForm</t>
+  </si>
+  <si>
+    <t>Overlay</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1418,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
@@ -1695,6 +1701,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" customHeight="1" spans="1:6">
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
